--- a/Honda_Logi/Excel_Format/包装費変動表.xlsx
+++ b/Honda_Logi/Excel_Format/包装費変動表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC08FD51-E179-4373-BD61-0D928B065CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97B2C89-5443-42E8-9C9A-15E1955E3E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{512732BF-C18F-4BAC-978A-EF9C15833451}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{512732BF-C18F-4BAC-978A-EF9C15833451}"/>
   </bookViews>
   <sheets>
     <sheet name="包装費変動表" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +164,14 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -267,12 +275,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -294,11 +305,23 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -310,7 +333,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -683,57 +707,178 @@
     <tabColor theme="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:LO4"/>
+  <dimension ref="A1:GS4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="6" width="11.125" style="5" customWidth="1"/>
-    <col min="7" max="11" width="11.125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="11.125" style="5" customWidth="1"/>
-    <col min="13" max="15" width="11.125" style="7" customWidth="1"/>
-    <col min="16" max="16" width="11.125" style="5" customWidth="1"/>
-    <col min="17" max="19" width="11.125" style="7" customWidth="1"/>
-    <col min="20" max="20" width="11.125" style="5" customWidth="1"/>
-    <col min="21" max="23" width="9" style="7"/>
-    <col min="24" max="24" width="9" style="5"/>
-    <col min="25" max="27" width="9" style="7"/>
-    <col min="28" max="28" width="9" style="5"/>
-    <col min="29" max="31" width="9" style="7"/>
-    <col min="32" max="32" width="9" style="5"/>
-    <col min="33" max="35" width="9" style="7"/>
-    <col min="36" max="36" width="9" style="5"/>
-    <col min="37" max="39" width="9" style="7"/>
-    <col min="40" max="40" width="9" style="5"/>
-    <col min="41" max="43" width="9" style="7"/>
-    <col min="44" max="44" width="9" style="5"/>
-    <col min="45" max="47" width="9" style="7"/>
-    <col min="48" max="48" width="9" style="5"/>
-    <col min="49" max="51" width="9" style="7"/>
-    <col min="52" max="52" width="9" style="5"/>
-    <col min="53" max="55" width="9" style="7"/>
-    <col min="56" max="56" width="9" style="5"/>
-    <col min="57" max="59" width="9" style="7"/>
-    <col min="60" max="60" width="9" style="5"/>
-    <col min="61" max="63" width="9" style="7"/>
-    <col min="64" max="64" width="9" style="5"/>
-    <col min="65" max="67" width="9" style="7"/>
-    <col min="68" max="327" width="9" style="5"/>
-    <col min="328" max="16384" width="9" style="1"/>
+    <col min="2" max="6" width="11.125" style="7" customWidth="1"/>
+    <col min="7" max="11" width="11.125" style="9" customWidth="1"/>
+    <col min="12" max="12" width="11.125" style="7" customWidth="1"/>
+    <col min="13" max="15" width="11.125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="11.125" style="7" customWidth="1"/>
+    <col min="17" max="19" width="11.125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="11.125" style="7" customWidth="1"/>
+    <col min="21" max="23" width="9" style="9"/>
+    <col min="24" max="24" width="9" style="7"/>
+    <col min="25" max="27" width="9" style="9"/>
+    <col min="28" max="28" width="9" style="7"/>
+    <col min="29" max="31" width="9" style="9"/>
+    <col min="32" max="32" width="9" style="7"/>
+    <col min="33" max="35" width="9" style="9"/>
+    <col min="36" max="36" width="9" style="7"/>
+    <col min="37" max="39" width="9" style="9"/>
+    <col min="40" max="40" width="9" style="7"/>
+    <col min="41" max="43" width="9" style="9"/>
+    <col min="44" max="44" width="9" style="7"/>
+    <col min="45" max="47" width="9" style="9"/>
+    <col min="48" max="48" width="9" style="7"/>
+    <col min="49" max="51" width="9" style="9"/>
+    <col min="52" max="52" width="9" style="7"/>
+    <col min="53" max="55" width="9" style="9"/>
+    <col min="56" max="56" width="9" style="7"/>
+    <col min="57" max="59" width="9" style="9"/>
+    <col min="60" max="60" width="9" style="7"/>
+    <col min="61" max="63" width="9" style="9"/>
+    <col min="64" max="64" width="9" style="7"/>
+    <col min="65" max="67" width="9" style="9"/>
+    <col min="68" max="68" width="9" style="7"/>
+    <col min="69" max="71" width="9" style="9"/>
+    <col min="72" max="72" width="9" style="7"/>
+    <col min="73" max="75" width="9" style="9"/>
+    <col min="76" max="76" width="9" style="7"/>
+    <col min="77" max="79" width="9" style="9"/>
+    <col min="80" max="80" width="9" style="7"/>
+    <col min="81" max="83" width="9" style="9"/>
+    <col min="84" max="84" width="9" style="7"/>
+    <col min="85" max="87" width="9" style="9"/>
+    <col min="88" max="88" width="9" style="7"/>
+    <col min="89" max="91" width="9" style="9"/>
+    <col min="92" max="92" width="9" style="7"/>
+    <col min="93" max="95" width="9" style="9"/>
+    <col min="96" max="96" width="9" style="7"/>
+    <col min="97" max="99" width="9" style="9"/>
+    <col min="100" max="100" width="9" style="7"/>
+    <col min="101" max="103" width="9" style="9"/>
+    <col min="104" max="104" width="9" style="7"/>
+    <col min="105" max="107" width="9" style="9"/>
+    <col min="108" max="108" width="9" style="7"/>
+    <col min="109" max="111" width="9" style="9"/>
+    <col min="112" max="112" width="9" style="7"/>
+    <col min="113" max="115" width="9" style="9"/>
+    <col min="116" max="116" width="9" style="7"/>
+    <col min="117" max="117" width="9" style="12"/>
+    <col min="118" max="119" width="9" style="9"/>
+    <col min="120" max="120" width="9" style="8"/>
+    <col min="121" max="121" width="9" style="12"/>
+    <col min="122" max="123" width="9" style="9"/>
+    <col min="124" max="124" width="9" style="8"/>
+    <col min="125" max="125" width="9" style="12"/>
+    <col min="126" max="127" width="9" style="9"/>
+    <col min="128" max="128" width="9" style="8"/>
+    <col min="129" max="129" width="9" style="12"/>
+    <col min="130" max="131" width="9" style="9"/>
+    <col min="132" max="132" width="9" style="8"/>
+    <col min="133" max="133" width="9" style="12"/>
+    <col min="134" max="135" width="9" style="9"/>
+    <col min="136" max="136" width="9" style="8"/>
+    <col min="137" max="137" width="9" style="12"/>
+    <col min="138" max="139" width="9" style="9"/>
+    <col min="140" max="140" width="9" style="8"/>
+    <col min="141" max="141" width="9" style="12"/>
+    <col min="142" max="143" width="9" style="9"/>
+    <col min="144" max="144" width="9" style="8"/>
+    <col min="145" max="145" width="9" style="12"/>
+    <col min="146" max="147" width="9" style="9"/>
+    <col min="148" max="148" width="9" style="8"/>
+    <col min="149" max="149" width="9" style="12"/>
+    <col min="150" max="151" width="9" style="9"/>
+    <col min="152" max="152" width="9" style="8"/>
+    <col min="153" max="153" width="9" style="12"/>
+    <col min="154" max="155" width="9" style="9"/>
+    <col min="156" max="156" width="9" style="8"/>
+    <col min="157" max="157" width="9" style="12"/>
+    <col min="158" max="159" width="9" style="9"/>
+    <col min="160" max="160" width="9" style="8"/>
+    <col min="161" max="161" width="9" style="12"/>
+    <col min="162" max="163" width="9" style="9"/>
+    <col min="164" max="164" width="9" style="8"/>
+    <col min="165" max="165" width="9" style="12"/>
+    <col min="166" max="167" width="9" style="9"/>
+    <col min="168" max="168" width="9" style="8"/>
+    <col min="169" max="169" width="9" style="12"/>
+    <col min="170" max="171" width="9" style="9"/>
+    <col min="172" max="172" width="9" style="8"/>
+    <col min="173" max="173" width="9" style="12"/>
+    <col min="174" max="175" width="9" style="9"/>
+    <col min="176" max="176" width="9" style="8"/>
+    <col min="177" max="177" width="9" style="12"/>
+    <col min="178" max="179" width="9" style="9"/>
+    <col min="180" max="180" width="9" style="8"/>
+    <col min="181" max="181" width="9" style="12"/>
+    <col min="182" max="183" width="9" style="9"/>
+    <col min="184" max="184" width="9" style="8"/>
+    <col min="185" max="185" width="9" style="12"/>
+    <col min="186" max="187" width="9" style="9"/>
+    <col min="188" max="188" width="9" style="8"/>
+    <col min="189" max="189" width="9" style="12"/>
+    <col min="190" max="191" width="9" style="9"/>
+    <col min="192" max="192" width="9" style="8"/>
+    <col min="193" max="193" width="9" style="12"/>
+    <col min="194" max="195" width="9" style="9"/>
+    <col min="196" max="196" width="9" style="8"/>
+    <col min="197" max="197" width="9" style="12"/>
+    <col min="198" max="199" width="9" style="9"/>
+    <col min="200" max="200" width="9" style="8"/>
+    <col min="201" max="201" width="9" style="7"/>
+    <col min="202" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
     </row>
     <row r="2" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B3" s="6"/>
@@ -746,24 +891,24 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="9" t="s">
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="9" t="s">
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="11"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="15"/>
     </row>
     <row r="4" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
@@ -799,37 +944,37 @@
       <c r="L4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="11" t="s">
         <v>12</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="Q4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="R4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="11" t="s">
         <v>12</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="V4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="11" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Honda_Logi/Excel_Format/包装費変動表.xlsx
+++ b/Honda_Logi/Excel_Format/包装費変動表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97B2C89-5443-42E8-9C9A-15E1955E3E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAF49CE-B661-4931-A4C1-E07B775A71C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{512732BF-C18F-4BAC-978A-EF9C15833451}"/>
+    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{512732BF-C18F-4BAC-978A-EF9C15833451}"/>
   </bookViews>
   <sheets>
     <sheet name="包装費変動表" sheetId="1" r:id="rId1"/>
@@ -283,7 +283,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -331,6 +331,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -711,129 +714,109 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="6" width="11.125" style="7" customWidth="1"/>
-    <col min="7" max="11" width="11.125" style="9" customWidth="1"/>
+    <col min="2" max="5" width="11.125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="8" customWidth="1"/>
+    <col min="7" max="11" width="11.125" style="16" customWidth="1"/>
     <col min="12" max="12" width="11.125" style="7" customWidth="1"/>
-    <col min="13" max="15" width="11.125" style="9" customWidth="1"/>
+    <col min="13" max="15" width="11.125" style="16" customWidth="1"/>
     <col min="16" max="16" width="11.125" style="7" customWidth="1"/>
-    <col min="17" max="19" width="11.125" style="9" customWidth="1"/>
+    <col min="17" max="19" width="11.125" style="16" customWidth="1"/>
     <col min="20" max="20" width="11.125" style="7" customWidth="1"/>
-    <col min="21" max="23" width="9" style="9"/>
+    <col min="21" max="23" width="9" style="16"/>
     <col min="24" max="24" width="9" style="7"/>
-    <col min="25" max="27" width="9" style="9"/>
+    <col min="25" max="27" width="9" style="16"/>
     <col min="28" max="28" width="9" style="7"/>
-    <col min="29" max="31" width="9" style="9"/>
+    <col min="29" max="31" width="9" style="16"/>
     <col min="32" max="32" width="9" style="7"/>
-    <col min="33" max="35" width="9" style="9"/>
+    <col min="33" max="35" width="9" style="16"/>
     <col min="36" max="36" width="9" style="7"/>
-    <col min="37" max="39" width="9" style="9"/>
+    <col min="37" max="39" width="9" style="16"/>
     <col min="40" max="40" width="9" style="7"/>
-    <col min="41" max="43" width="9" style="9"/>
+    <col min="41" max="43" width="9" style="16"/>
     <col min="44" max="44" width="9" style="7"/>
-    <col min="45" max="47" width="9" style="9"/>
+    <col min="45" max="47" width="9" style="16"/>
     <col min="48" max="48" width="9" style="7"/>
-    <col min="49" max="51" width="9" style="9"/>
+    <col min="49" max="51" width="9" style="16"/>
     <col min="52" max="52" width="9" style="7"/>
-    <col min="53" max="55" width="9" style="9"/>
+    <col min="53" max="55" width="9" style="16"/>
     <col min="56" max="56" width="9" style="7"/>
-    <col min="57" max="59" width="9" style="9"/>
+    <col min="57" max="59" width="9" style="16"/>
     <col min="60" max="60" width="9" style="7"/>
-    <col min="61" max="63" width="9" style="9"/>
+    <col min="61" max="63" width="9" style="16"/>
     <col min="64" max="64" width="9" style="7"/>
-    <col min="65" max="67" width="9" style="9"/>
+    <col min="65" max="67" width="9" style="16"/>
     <col min="68" max="68" width="9" style="7"/>
-    <col min="69" max="71" width="9" style="9"/>
+    <col min="69" max="71" width="9" style="16"/>
     <col min="72" max="72" width="9" style="7"/>
-    <col min="73" max="75" width="9" style="9"/>
+    <col min="73" max="75" width="9" style="16"/>
     <col min="76" max="76" width="9" style="7"/>
-    <col min="77" max="79" width="9" style="9"/>
+    <col min="77" max="79" width="9" style="16"/>
     <col min="80" max="80" width="9" style="7"/>
-    <col min="81" max="83" width="9" style="9"/>
+    <col min="81" max="83" width="9" style="16"/>
     <col min="84" max="84" width="9" style="7"/>
-    <col min="85" max="87" width="9" style="9"/>
+    <col min="85" max="87" width="9" style="16"/>
     <col min="88" max="88" width="9" style="7"/>
-    <col min="89" max="91" width="9" style="9"/>
+    <col min="89" max="91" width="9" style="16"/>
     <col min="92" max="92" width="9" style="7"/>
-    <col min="93" max="95" width="9" style="9"/>
+    <col min="93" max="95" width="9" style="16"/>
     <col min="96" max="96" width="9" style="7"/>
-    <col min="97" max="99" width="9" style="9"/>
+    <col min="97" max="99" width="9" style="16"/>
     <col min="100" max="100" width="9" style="7"/>
-    <col min="101" max="103" width="9" style="9"/>
+    <col min="101" max="103" width="9" style="16"/>
     <col min="104" max="104" width="9" style="7"/>
-    <col min="105" max="107" width="9" style="9"/>
+    <col min="105" max="107" width="9" style="16"/>
     <col min="108" max="108" width="9" style="7"/>
-    <col min="109" max="111" width="9" style="9"/>
+    <col min="109" max="111" width="9" style="16"/>
     <col min="112" max="112" width="9" style="7"/>
-    <col min="113" max="115" width="9" style="9"/>
+    <col min="113" max="115" width="9" style="16"/>
     <col min="116" max="116" width="9" style="7"/>
-    <col min="117" max="117" width="9" style="12"/>
-    <col min="118" max="119" width="9" style="9"/>
-    <col min="120" max="120" width="9" style="8"/>
-    <col min="121" max="121" width="9" style="12"/>
-    <col min="122" max="123" width="9" style="9"/>
-    <col min="124" max="124" width="9" style="8"/>
-    <col min="125" max="125" width="9" style="12"/>
-    <col min="126" max="127" width="9" style="9"/>
-    <col min="128" max="128" width="9" style="8"/>
-    <col min="129" max="129" width="9" style="12"/>
-    <col min="130" max="131" width="9" style="9"/>
-    <col min="132" max="132" width="9" style="8"/>
-    <col min="133" max="133" width="9" style="12"/>
-    <col min="134" max="135" width="9" style="9"/>
-    <col min="136" max="136" width="9" style="8"/>
-    <col min="137" max="137" width="9" style="12"/>
-    <col min="138" max="139" width="9" style="9"/>
-    <col min="140" max="140" width="9" style="8"/>
-    <col min="141" max="141" width="9" style="12"/>
-    <col min="142" max="143" width="9" style="9"/>
-    <col min="144" max="144" width="9" style="8"/>
-    <col min="145" max="145" width="9" style="12"/>
-    <col min="146" max="147" width="9" style="9"/>
-    <col min="148" max="148" width="9" style="8"/>
-    <col min="149" max="149" width="9" style="12"/>
-    <col min="150" max="151" width="9" style="9"/>
-    <col min="152" max="152" width="9" style="8"/>
-    <col min="153" max="153" width="9" style="12"/>
-    <col min="154" max="155" width="9" style="9"/>
-    <col min="156" max="156" width="9" style="8"/>
-    <col min="157" max="157" width="9" style="12"/>
-    <col min="158" max="159" width="9" style="9"/>
-    <col min="160" max="160" width="9" style="8"/>
-    <col min="161" max="161" width="9" style="12"/>
-    <col min="162" max="163" width="9" style="9"/>
-    <col min="164" max="164" width="9" style="8"/>
-    <col min="165" max="165" width="9" style="12"/>
-    <col min="166" max="167" width="9" style="9"/>
-    <col min="168" max="168" width="9" style="8"/>
-    <col min="169" max="169" width="9" style="12"/>
-    <col min="170" max="171" width="9" style="9"/>
-    <col min="172" max="172" width="9" style="8"/>
-    <col min="173" max="173" width="9" style="12"/>
-    <col min="174" max="175" width="9" style="9"/>
-    <col min="176" max="176" width="9" style="8"/>
-    <col min="177" max="177" width="9" style="12"/>
-    <col min="178" max="179" width="9" style="9"/>
-    <col min="180" max="180" width="9" style="8"/>
-    <col min="181" max="181" width="9" style="12"/>
-    <col min="182" max="183" width="9" style="9"/>
-    <col min="184" max="184" width="9" style="8"/>
-    <col min="185" max="185" width="9" style="12"/>
-    <col min="186" max="187" width="9" style="9"/>
-    <col min="188" max="188" width="9" style="8"/>
-    <col min="189" max="189" width="9" style="12"/>
-    <col min="190" max="191" width="9" style="9"/>
-    <col min="192" max="192" width="9" style="8"/>
-    <col min="193" max="193" width="9" style="12"/>
-    <col min="194" max="195" width="9" style="9"/>
-    <col min="196" max="196" width="9" style="8"/>
-    <col min="197" max="197" width="9" style="12"/>
-    <col min="198" max="199" width="9" style="9"/>
+    <col min="117" max="119" width="9" style="16"/>
+    <col min="120" max="120" width="9" style="7"/>
+    <col min="121" max="123" width="9" style="16"/>
+    <col min="124" max="124" width="9" style="7"/>
+    <col min="125" max="127" width="9" style="16"/>
+    <col min="128" max="128" width="9" style="7"/>
+    <col min="129" max="131" width="9" style="16"/>
+    <col min="132" max="132" width="9" style="7"/>
+    <col min="133" max="135" width="9" style="16"/>
+    <col min="136" max="136" width="9" style="7"/>
+    <col min="137" max="139" width="9" style="16"/>
+    <col min="140" max="140" width="9" style="7"/>
+    <col min="141" max="143" width="9" style="16"/>
+    <col min="144" max="144" width="9" style="7"/>
+    <col min="145" max="147" width="9" style="16"/>
+    <col min="148" max="148" width="9" style="7"/>
+    <col min="149" max="151" width="9" style="16"/>
+    <col min="152" max="152" width="9" style="7"/>
+    <col min="153" max="155" width="9" style="16"/>
+    <col min="156" max="156" width="9" style="7"/>
+    <col min="157" max="159" width="9" style="16"/>
+    <col min="160" max="160" width="9" style="7"/>
+    <col min="161" max="163" width="9" style="16"/>
+    <col min="164" max="164" width="9" style="7"/>
+    <col min="165" max="167" width="9" style="16"/>
+    <col min="168" max="168" width="9" style="7"/>
+    <col min="169" max="171" width="9" style="16"/>
+    <col min="172" max="172" width="9" style="7"/>
+    <col min="173" max="175" width="9" style="16"/>
+    <col min="176" max="176" width="9" style="7"/>
+    <col min="177" max="179" width="9" style="16"/>
+    <col min="180" max="180" width="9" style="7"/>
+    <col min="181" max="183" width="9" style="16"/>
+    <col min="184" max="184" width="9" style="7"/>
+    <col min="185" max="187" width="9" style="16"/>
+    <col min="188" max="188" width="9" style="7"/>
+    <col min="189" max="191" width="9" style="16"/>
+    <col min="192" max="192" width="9" style="7"/>
+    <col min="193" max="195" width="9" style="16"/>
+    <col min="196" max="196" width="9" style="7"/>
+    <col min="197" max="199" width="9" style="16"/>
     <col min="200" max="200" width="9" style="8"/>
     <col min="201" max="201" width="9" style="7"/>
     <col min="202" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:199" x14ac:dyDescent="0.4">
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -856,8 +839,160 @@
       <c r="U1" s="10"/>
       <c r="V1" s="10"/>
       <c r="W1" s="10"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AS1" s="9"/>
+      <c r="AT1" s="9"/>
+      <c r="AU1" s="9"/>
+      <c r="AW1" s="9"/>
+      <c r="AX1" s="9"/>
+      <c r="AY1" s="9"/>
+      <c r="BA1" s="9"/>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BE1" s="9"/>
+      <c r="BF1" s="9"/>
+      <c r="BG1" s="9"/>
+      <c r="BI1" s="9"/>
+      <c r="BJ1" s="9"/>
+      <c r="BK1" s="9"/>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="9"/>
+      <c r="BO1" s="9"/>
+      <c r="BQ1" s="9"/>
+      <c r="BR1" s="9"/>
+      <c r="BS1" s="9"/>
+      <c r="BU1" s="9"/>
+      <c r="BV1" s="9"/>
+      <c r="BW1" s="9"/>
+      <c r="BY1" s="9"/>
+      <c r="BZ1" s="9"/>
+      <c r="CA1" s="9"/>
+      <c r="CC1" s="9"/>
+      <c r="CD1" s="9"/>
+      <c r="CE1" s="9"/>
+      <c r="CG1" s="9"/>
+      <c r="CH1" s="9"/>
+      <c r="CI1" s="9"/>
+      <c r="CK1" s="9"/>
+      <c r="CL1" s="9"/>
+      <c r="CM1" s="9"/>
+      <c r="CO1" s="9"/>
+      <c r="CP1" s="9"/>
+      <c r="CQ1" s="9"/>
+      <c r="CS1" s="9"/>
+      <c r="CT1" s="9"/>
+      <c r="CU1" s="9"/>
+      <c r="CW1" s="9"/>
+      <c r="CX1" s="9"/>
+      <c r="CY1" s="9"/>
+      <c r="DA1" s="9"/>
+      <c r="DB1" s="9"/>
+      <c r="DC1" s="9"/>
+      <c r="DE1" s="9"/>
+      <c r="DF1" s="9"/>
+      <c r="DG1" s="9"/>
+      <c r="DI1" s="9"/>
+      <c r="DJ1" s="9"/>
+      <c r="DK1" s="9"/>
+      <c r="DM1" s="12"/>
+      <c r="DN1" s="9"/>
+      <c r="DO1" s="9"/>
+      <c r="DP1" s="8"/>
+      <c r="DQ1" s="12"/>
+      <c r="DR1" s="9"/>
+      <c r="DS1" s="9"/>
+      <c r="DT1" s="8"/>
+      <c r="DU1" s="12"/>
+      <c r="DV1" s="9"/>
+      <c r="DW1" s="9"/>
+      <c r="DX1" s="8"/>
+      <c r="DY1" s="12"/>
+      <c r="DZ1" s="9"/>
+      <c r="EA1" s="9"/>
+      <c r="EB1" s="8"/>
+      <c r="EC1" s="12"/>
+      <c r="ED1" s="9"/>
+      <c r="EE1" s="9"/>
+      <c r="EF1" s="8"/>
+      <c r="EG1" s="12"/>
+      <c r="EH1" s="9"/>
+      <c r="EI1" s="9"/>
+      <c r="EJ1" s="8"/>
+      <c r="EK1" s="12"/>
+      <c r="EL1" s="9"/>
+      <c r="EM1" s="9"/>
+      <c r="EN1" s="8"/>
+      <c r="EO1" s="12"/>
+      <c r="EP1" s="9"/>
+      <c r="EQ1" s="9"/>
+      <c r="ER1" s="8"/>
+      <c r="ES1" s="12"/>
+      <c r="ET1" s="9"/>
+      <c r="EU1" s="9"/>
+      <c r="EV1" s="8"/>
+      <c r="EW1" s="12"/>
+      <c r="EX1" s="9"/>
+      <c r="EY1" s="9"/>
+      <c r="EZ1" s="8"/>
+      <c r="FA1" s="12"/>
+      <c r="FB1" s="9"/>
+      <c r="FC1" s="9"/>
+      <c r="FD1" s="8"/>
+      <c r="FE1" s="12"/>
+      <c r="FF1" s="9"/>
+      <c r="FG1" s="9"/>
+      <c r="FH1" s="8"/>
+      <c r="FI1" s="12"/>
+      <c r="FJ1" s="9"/>
+      <c r="FK1" s="9"/>
+      <c r="FL1" s="8"/>
+      <c r="FM1" s="12"/>
+      <c r="FN1" s="9"/>
+      <c r="FO1" s="9"/>
+      <c r="FP1" s="8"/>
+      <c r="FQ1" s="12"/>
+      <c r="FR1" s="9"/>
+      <c r="FS1" s="9"/>
+      <c r="FT1" s="8"/>
+      <c r="FU1" s="12"/>
+      <c r="FV1" s="9"/>
+      <c r="FW1" s="9"/>
+      <c r="FX1" s="8"/>
+      <c r="FY1" s="12"/>
+      <c r="FZ1" s="9"/>
+      <c r="GA1" s="9"/>
+      <c r="GB1" s="8"/>
+      <c r="GC1" s="12"/>
+      <c r="GD1" s="9"/>
+      <c r="GE1" s="9"/>
+      <c r="GF1" s="8"/>
+      <c r="GG1" s="12"/>
+      <c r="GH1" s="9"/>
+      <c r="GI1" s="9"/>
+      <c r="GJ1" s="8"/>
+      <c r="GK1" s="12"/>
+      <c r="GL1" s="9"/>
+      <c r="GM1" s="9"/>
+      <c r="GN1" s="8"/>
+      <c r="GO1" s="12"/>
+      <c r="GP1" s="9"/>
+      <c r="GQ1" s="9"/>
     </row>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:199" x14ac:dyDescent="0.4">
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -879,8 +1014,160 @@
       <c r="U2" s="10"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="9"/>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BQ2" s="9"/>
+      <c r="BR2" s="9"/>
+      <c r="BS2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+      <c r="BW2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="9"/>
+      <c r="CA2" s="9"/>
+      <c r="CC2" s="9"/>
+      <c r="CD2" s="9"/>
+      <c r="CE2" s="9"/>
+      <c r="CG2" s="9"/>
+      <c r="CH2" s="9"/>
+      <c r="CI2" s="9"/>
+      <c r="CK2" s="9"/>
+      <c r="CL2" s="9"/>
+      <c r="CM2" s="9"/>
+      <c r="CO2" s="9"/>
+      <c r="CP2" s="9"/>
+      <c r="CQ2" s="9"/>
+      <c r="CS2" s="9"/>
+      <c r="CT2" s="9"/>
+      <c r="CU2" s="9"/>
+      <c r="CW2" s="9"/>
+      <c r="CX2" s="9"/>
+      <c r="CY2" s="9"/>
+      <c r="DA2" s="9"/>
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DE2" s="9"/>
+      <c r="DF2" s="9"/>
+      <c r="DG2" s="9"/>
+      <c r="DI2" s="9"/>
+      <c r="DJ2" s="9"/>
+      <c r="DK2" s="9"/>
+      <c r="DM2" s="12"/>
+      <c r="DN2" s="9"/>
+      <c r="DO2" s="9"/>
+      <c r="DP2" s="8"/>
+      <c r="DQ2" s="12"/>
+      <c r="DR2" s="9"/>
+      <c r="DS2" s="9"/>
+      <c r="DT2" s="8"/>
+      <c r="DU2" s="12"/>
+      <c r="DV2" s="9"/>
+      <c r="DW2" s="9"/>
+      <c r="DX2" s="8"/>
+      <c r="DY2" s="12"/>
+      <c r="DZ2" s="9"/>
+      <c r="EA2" s="9"/>
+      <c r="EB2" s="8"/>
+      <c r="EC2" s="12"/>
+      <c r="ED2" s="9"/>
+      <c r="EE2" s="9"/>
+      <c r="EF2" s="8"/>
+      <c r="EG2" s="12"/>
+      <c r="EH2" s="9"/>
+      <c r="EI2" s="9"/>
+      <c r="EJ2" s="8"/>
+      <c r="EK2" s="12"/>
+      <c r="EL2" s="9"/>
+      <c r="EM2" s="9"/>
+      <c r="EN2" s="8"/>
+      <c r="EO2" s="12"/>
+      <c r="EP2" s="9"/>
+      <c r="EQ2" s="9"/>
+      <c r="ER2" s="8"/>
+      <c r="ES2" s="12"/>
+      <c r="ET2" s="9"/>
+      <c r="EU2" s="9"/>
+      <c r="EV2" s="8"/>
+      <c r="EW2" s="12"/>
+      <c r="EX2" s="9"/>
+      <c r="EY2" s="9"/>
+      <c r="EZ2" s="8"/>
+      <c r="FA2" s="12"/>
+      <c r="FB2" s="9"/>
+      <c r="FC2" s="9"/>
+      <c r="FD2" s="8"/>
+      <c r="FE2" s="12"/>
+      <c r="FF2" s="9"/>
+      <c r="FG2" s="9"/>
+      <c r="FH2" s="8"/>
+      <c r="FI2" s="12"/>
+      <c r="FJ2" s="9"/>
+      <c r="FK2" s="9"/>
+      <c r="FL2" s="8"/>
+      <c r="FM2" s="12"/>
+      <c r="FN2" s="9"/>
+      <c r="FO2" s="9"/>
+      <c r="FP2" s="8"/>
+      <c r="FQ2" s="12"/>
+      <c r="FR2" s="9"/>
+      <c r="FS2" s="9"/>
+      <c r="FT2" s="8"/>
+      <c r="FU2" s="12"/>
+      <c r="FV2" s="9"/>
+      <c r="FW2" s="9"/>
+      <c r="FX2" s="8"/>
+      <c r="FY2" s="12"/>
+      <c r="FZ2" s="9"/>
+      <c r="GA2" s="9"/>
+      <c r="GB2" s="8"/>
+      <c r="GC2" s="12"/>
+      <c r="GD2" s="9"/>
+      <c r="GE2" s="9"/>
+      <c r="GF2" s="8"/>
+      <c r="GG2" s="12"/>
+      <c r="GH2" s="9"/>
+      <c r="GI2" s="9"/>
+      <c r="GJ2" s="8"/>
+      <c r="GK2" s="12"/>
+      <c r="GL2" s="9"/>
+      <c r="GM2" s="9"/>
+      <c r="GN2" s="8"/>
+      <c r="GO2" s="12"/>
+      <c r="GP2" s="9"/>
+      <c r="GQ2" s="9"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:199" x14ac:dyDescent="0.4">
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -909,8 +1196,160 @@
       <c r="U3" s="14"/>
       <c r="V3" s="14"/>
       <c r="W3" s="15"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
+      <c r="AW3" s="9"/>
+      <c r="AX3" s="9"/>
+      <c r="AY3" s="9"/>
+      <c r="BA3" s="9"/>
+      <c r="BB3" s="9"/>
+      <c r="BC3" s="9"/>
+      <c r="BE3" s="9"/>
+      <c r="BF3" s="9"/>
+      <c r="BG3" s="9"/>
+      <c r="BI3" s="9"/>
+      <c r="BJ3" s="9"/>
+      <c r="BK3" s="9"/>
+      <c r="BM3" s="9"/>
+      <c r="BN3" s="9"/>
+      <c r="BO3" s="9"/>
+      <c r="BQ3" s="9"/>
+      <c r="BR3" s="9"/>
+      <c r="BS3" s="9"/>
+      <c r="BU3" s="9"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BY3" s="9"/>
+      <c r="BZ3" s="9"/>
+      <c r="CA3" s="9"/>
+      <c r="CC3" s="9"/>
+      <c r="CD3" s="9"/>
+      <c r="CE3" s="9"/>
+      <c r="CG3" s="9"/>
+      <c r="CH3" s="9"/>
+      <c r="CI3" s="9"/>
+      <c r="CK3" s="9"/>
+      <c r="CL3" s="9"/>
+      <c r="CM3" s="9"/>
+      <c r="CO3" s="9"/>
+      <c r="CP3" s="9"/>
+      <c r="CQ3" s="9"/>
+      <c r="CS3" s="9"/>
+      <c r="CT3" s="9"/>
+      <c r="CU3" s="9"/>
+      <c r="CW3" s="9"/>
+      <c r="CX3" s="9"/>
+      <c r="CY3" s="9"/>
+      <c r="DA3" s="9"/>
+      <c r="DB3" s="9"/>
+      <c r="DC3" s="9"/>
+      <c r="DE3" s="9"/>
+      <c r="DF3" s="9"/>
+      <c r="DG3" s="9"/>
+      <c r="DI3" s="9"/>
+      <c r="DJ3" s="9"/>
+      <c r="DK3" s="9"/>
+      <c r="DM3" s="12"/>
+      <c r="DN3" s="9"/>
+      <c r="DO3" s="9"/>
+      <c r="DP3" s="8"/>
+      <c r="DQ3" s="12"/>
+      <c r="DR3" s="9"/>
+      <c r="DS3" s="9"/>
+      <c r="DT3" s="8"/>
+      <c r="DU3" s="12"/>
+      <c r="DV3" s="9"/>
+      <c r="DW3" s="9"/>
+      <c r="DX3" s="8"/>
+      <c r="DY3" s="12"/>
+      <c r="DZ3" s="9"/>
+      <c r="EA3" s="9"/>
+      <c r="EB3" s="8"/>
+      <c r="EC3" s="12"/>
+      <c r="ED3" s="9"/>
+      <c r="EE3" s="9"/>
+      <c r="EF3" s="8"/>
+      <c r="EG3" s="12"/>
+      <c r="EH3" s="9"/>
+      <c r="EI3" s="9"/>
+      <c r="EJ3" s="8"/>
+      <c r="EK3" s="12"/>
+      <c r="EL3" s="9"/>
+      <c r="EM3" s="9"/>
+      <c r="EN3" s="8"/>
+      <c r="EO3" s="12"/>
+      <c r="EP3" s="9"/>
+      <c r="EQ3" s="9"/>
+      <c r="ER3" s="8"/>
+      <c r="ES3" s="12"/>
+      <c r="ET3" s="9"/>
+      <c r="EU3" s="9"/>
+      <c r="EV3" s="8"/>
+      <c r="EW3" s="12"/>
+      <c r="EX3" s="9"/>
+      <c r="EY3" s="9"/>
+      <c r="EZ3" s="8"/>
+      <c r="FA3" s="12"/>
+      <c r="FB3" s="9"/>
+      <c r="FC3" s="9"/>
+      <c r="FD3" s="8"/>
+      <c r="FE3" s="12"/>
+      <c r="FF3" s="9"/>
+      <c r="FG3" s="9"/>
+      <c r="FH3" s="8"/>
+      <c r="FI3" s="12"/>
+      <c r="FJ3" s="9"/>
+      <c r="FK3" s="9"/>
+      <c r="FL3" s="8"/>
+      <c r="FM3" s="12"/>
+      <c r="FN3" s="9"/>
+      <c r="FO3" s="9"/>
+      <c r="FP3" s="8"/>
+      <c r="FQ3" s="12"/>
+      <c r="FR3" s="9"/>
+      <c r="FS3" s="9"/>
+      <c r="FT3" s="8"/>
+      <c r="FU3" s="12"/>
+      <c r="FV3" s="9"/>
+      <c r="FW3" s="9"/>
+      <c r="FX3" s="8"/>
+      <c r="FY3" s="12"/>
+      <c r="FZ3" s="9"/>
+      <c r="GA3" s="9"/>
+      <c r="GB3" s="8"/>
+      <c r="GC3" s="12"/>
+      <c r="GD3" s="9"/>
+      <c r="GE3" s="9"/>
+      <c r="GF3" s="8"/>
+      <c r="GG3" s="12"/>
+      <c r="GH3" s="9"/>
+      <c r="GI3" s="9"/>
+      <c r="GJ3" s="8"/>
+      <c r="GK3" s="12"/>
+      <c r="GL3" s="9"/>
+      <c r="GM3" s="9"/>
+      <c r="GN3" s="8"/>
+      <c r="GO3" s="12"/>
+      <c r="GP3" s="9"/>
+      <c r="GQ3" s="9"/>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:199" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
@@ -977,6 +1416,158 @@
       <c r="W4" s="11" t="s">
         <v>12</v>
       </c>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="9"/>
+      <c r="AW4" s="9"/>
+      <c r="AX4" s="9"/>
+      <c r="AY4" s="9"/>
+      <c r="BA4" s="9"/>
+      <c r="BB4" s="9"/>
+      <c r="BC4" s="9"/>
+      <c r="BE4" s="9"/>
+      <c r="BF4" s="9"/>
+      <c r="BG4" s="9"/>
+      <c r="BI4" s="9"/>
+      <c r="BJ4" s="9"/>
+      <c r="BK4" s="9"/>
+      <c r="BM4" s="9"/>
+      <c r="BN4" s="9"/>
+      <c r="BO4" s="9"/>
+      <c r="BQ4" s="9"/>
+      <c r="BR4" s="9"/>
+      <c r="BS4" s="9"/>
+      <c r="BU4" s="9"/>
+      <c r="BV4" s="9"/>
+      <c r="BW4" s="9"/>
+      <c r="BY4" s="9"/>
+      <c r="BZ4" s="9"/>
+      <c r="CA4" s="9"/>
+      <c r="CC4" s="9"/>
+      <c r="CD4" s="9"/>
+      <c r="CE4" s="9"/>
+      <c r="CG4" s="9"/>
+      <c r="CH4" s="9"/>
+      <c r="CI4" s="9"/>
+      <c r="CK4" s="9"/>
+      <c r="CL4" s="9"/>
+      <c r="CM4" s="9"/>
+      <c r="CO4" s="9"/>
+      <c r="CP4" s="9"/>
+      <c r="CQ4" s="9"/>
+      <c r="CS4" s="9"/>
+      <c r="CT4" s="9"/>
+      <c r="CU4" s="9"/>
+      <c r="CW4" s="9"/>
+      <c r="CX4" s="9"/>
+      <c r="CY4" s="9"/>
+      <c r="DA4" s="9"/>
+      <c r="DB4" s="9"/>
+      <c r="DC4" s="9"/>
+      <c r="DE4" s="9"/>
+      <c r="DF4" s="9"/>
+      <c r="DG4" s="9"/>
+      <c r="DI4" s="9"/>
+      <c r="DJ4" s="9"/>
+      <c r="DK4" s="9"/>
+      <c r="DM4" s="12"/>
+      <c r="DN4" s="9"/>
+      <c r="DO4" s="9"/>
+      <c r="DP4" s="8"/>
+      <c r="DQ4" s="12"/>
+      <c r="DR4" s="9"/>
+      <c r="DS4" s="9"/>
+      <c r="DT4" s="8"/>
+      <c r="DU4" s="12"/>
+      <c r="DV4" s="9"/>
+      <c r="DW4" s="9"/>
+      <c r="DX4" s="8"/>
+      <c r="DY4" s="12"/>
+      <c r="DZ4" s="9"/>
+      <c r="EA4" s="9"/>
+      <c r="EB4" s="8"/>
+      <c r="EC4" s="12"/>
+      <c r="ED4" s="9"/>
+      <c r="EE4" s="9"/>
+      <c r="EF4" s="8"/>
+      <c r="EG4" s="12"/>
+      <c r="EH4" s="9"/>
+      <c r="EI4" s="9"/>
+      <c r="EJ4" s="8"/>
+      <c r="EK4" s="12"/>
+      <c r="EL4" s="9"/>
+      <c r="EM4" s="9"/>
+      <c r="EN4" s="8"/>
+      <c r="EO4" s="12"/>
+      <c r="EP4" s="9"/>
+      <c r="EQ4" s="9"/>
+      <c r="ER4" s="8"/>
+      <c r="ES4" s="12"/>
+      <c r="ET4" s="9"/>
+      <c r="EU4" s="9"/>
+      <c r="EV4" s="8"/>
+      <c r="EW4" s="12"/>
+      <c r="EX4" s="9"/>
+      <c r="EY4" s="9"/>
+      <c r="EZ4" s="8"/>
+      <c r="FA4" s="12"/>
+      <c r="FB4" s="9"/>
+      <c r="FC4" s="9"/>
+      <c r="FD4" s="8"/>
+      <c r="FE4" s="12"/>
+      <c r="FF4" s="9"/>
+      <c r="FG4" s="9"/>
+      <c r="FH4" s="8"/>
+      <c r="FI4" s="12"/>
+      <c r="FJ4" s="9"/>
+      <c r="FK4" s="9"/>
+      <c r="FL4" s="8"/>
+      <c r="FM4" s="12"/>
+      <c r="FN4" s="9"/>
+      <c r="FO4" s="9"/>
+      <c r="FP4" s="8"/>
+      <c r="FQ4" s="12"/>
+      <c r="FR4" s="9"/>
+      <c r="FS4" s="9"/>
+      <c r="FT4" s="8"/>
+      <c r="FU4" s="12"/>
+      <c r="FV4" s="9"/>
+      <c r="FW4" s="9"/>
+      <c r="FX4" s="8"/>
+      <c r="FY4" s="12"/>
+      <c r="FZ4" s="9"/>
+      <c r="GA4" s="9"/>
+      <c r="GB4" s="8"/>
+      <c r="GC4" s="12"/>
+      <c r="GD4" s="9"/>
+      <c r="GE4" s="9"/>
+      <c r="GF4" s="8"/>
+      <c r="GG4" s="12"/>
+      <c r="GH4" s="9"/>
+      <c r="GI4" s="9"/>
+      <c r="GJ4" s="8"/>
+      <c r="GK4" s="12"/>
+      <c r="GL4" s="9"/>
+      <c r="GM4" s="9"/>
+      <c r="GN4" s="8"/>
+      <c r="GO4" s="12"/>
+      <c r="GP4" s="9"/>
+      <c r="GQ4" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
